--- a/artfynd/A 30229-2023 artfynd.xlsx
+++ b/artfynd/A 30229-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30229-2023 artfynd.xlsx
+++ b/artfynd/A 30229-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126489565</v>
+      </c>
+      <c r="B3" t="n">
+        <v>44801</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Väg korsar Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572881</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6532873</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ove Sjögrund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ove Sjögrund, Ingrid Sjögrund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30229-2023 artfynd.xlsx
+++ b/artfynd/A 30229-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>110830047</v>
       </c>
       <c r="B2" t="n">
-        <v>42507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572881.4309825685</v>
+        <v>572881</v>
       </c>
       <c r="R2" t="n">
-        <v>6532873.133908973</v>
+        <v>6532873</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,19 +756,9 @@
           <t>2023-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,11 +789,11 @@
         <v>126489565</v>
       </c>
       <c r="B3" t="n">
-        <v>44801</v>
+        <v>45044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -909,6 +894,228 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126785889</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43219</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201028</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Thymelicus lineola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väg korsar Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572881</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6532873</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ove Sjögrund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ove Sjögrund, Ingrid Sjögrund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126489552</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väg korsar Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572881</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6532873</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ove Sjögrund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ove Sjögrund, Ingrid Sjögrund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30229-2023 artfynd.xlsx
+++ b/artfynd/A 30229-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110830047</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126489565</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126785889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126489552</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>